--- a/wiki/reports/daily/2026-10-13_일일보고.xlsx
+++ b/wiki/reports/daily/2026-10-13_일일보고.xlsx
@@ -155,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,6 +194,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -624,7 +627,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-10-13 07:56   |   전일: 10월 12일   |   월평균 기준: 이전 작업일 6일 평균   |   10월 누적 작업일: 7일</t>
+          <t>생성: 2026-10-13 16:00   |   전일: 10월 12일   |   월평균 기준: 이전 작업일 6일 평균   |   10월 누적 작업일: 7일</t>
         </is>
       </c>
     </row>
@@ -686,25 +689,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>67</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-62</v>
+        <v>-32</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-0.9253731343283582</v>
+        <v>-0.4776119402985075</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>51.8</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-46.83333333333334</v>
+        <v>-16.83333333333334</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-0.9035369774919614</v>
+        <v>-0.3247588424437299</v>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
     </row>
@@ -715,29 +718,29 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>925</v>
+        <v>8002</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>14819</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-13894</v>
+        <v>-6817</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-0.9375801336122546</v>
+        <v>-0.4600175450435252</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>12388.2</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-11463.16666666667</v>
+        <v>-4386.166666666666</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>-0.9253319700251584</v>
+        <v>-0.3540609990716947</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>0:15:25</t>
+          <t>2:13:22</t>
         </is>
       </c>
     </row>
@@ -748,13 +751,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
@@ -765,10 +768,10 @@
         <v>32.8</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>-31.83333333333334</v>
+        <v>-14.83333333333334</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-0.9695431472081218</v>
+        <v>-0.4517766497461929</v>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
     </row>
@@ -779,13 +782,13 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>225</v>
+        <v>12720</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>225</v>
+        <v>12720</v>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -795,129 +798,129 @@
       <c r="F7" s="9" t="n">
         <v>9762.299999999999</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>-9537.333333333334</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>-0.9769522313654523</v>
+      <c r="G7" s="12" t="n">
+        <v>2957.666666666666</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0.3029671868064328</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>0:03:45</t>
+          <t>3:32:00</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>합계  수량 (개)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>67</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>-61</v>
+        <v>-14</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-0.9104477611940298</v>
+        <v>-0.208955223880597</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>84.7</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-78.66666666666667</v>
+        <v>-31.66666666666667</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>-0.9291338582677166</v>
+        <v>-0.3740157480314961</v>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>합계  가공시간 (초)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1150</v>
+        <v>20722</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>14819</v>
       </c>
-      <c r="D9" s="7" t="n">
-        <v>-13669</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>-0.9223969228692894</v>
+      <c r="D9" s="12" t="n">
+        <v>5903</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0.3983399689587692</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>22150.5</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-21000.5</v>
+        <v>-1428.5</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>-0.9480824360623914</v>
+        <v>-0.06449064355206428</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>0:19:10</t>
+          <t>5:45:22</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>합계  금액</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>67</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>-61</v>
+        <v>-14</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-0.9104477611940298</v>
+        <v>-0.208955223880597</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>84.7</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-78.66666666666667</v>
+        <v>-31.66666666666667</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>-0.9291338582677166</v>
+        <v>-0.3740157480314961</v>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>10월 누적  (7일 / 13일 중 작업일)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="16" t="n">
-        <v>514</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>134053</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>514</v>
-      </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="17" t="n">
+        <v>561</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>153625</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>561</v>
+      </c>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="16" t="n"/>
+      <c r="I11" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -935,7 +938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -959,271 +962,722 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>■ FAST GRIND</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G3" s="18" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I3" s="18" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J3" s="18" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K3" s="18" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="n">
+      <c r="A4" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>볼</t>
         </is>
       </c>
-      <c r="C4" s="19" t="n">
+      <c r="C4" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D4" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr"/>
+      <c r="I4" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="22" t="n">
+        <v>740</v>
+      </c>
+      <c r="K4" s="20" t="inlineStr">
+        <is>
+          <t>0:12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>뮤</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr">
-        <is>
-          <t>0040</t>
-        </is>
-      </c>
-      <c r="H4" s="19" t="inlineStr"/>
-      <c r="I4" s="21" t="n">
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>0165</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="22" t="n">
+        <v>234</v>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>0:03:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>0106 ㅋㅌ</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" s="22" t="n">
+        <v>2420</v>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>0:40:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="J7" s="22" t="n">
+        <v>3872</v>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>1:04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="J4" s="21" t="n">
-        <v>925</v>
-      </c>
-      <c r="K4" s="19" t="inlineStr">
-        <is>
-          <t>0:15:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>0124</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr"/>
+      <c r="I8" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>736</v>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>0:12:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>FAST GRIND 소계</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n"/>
-      <c r="I5" s="16" t="n">
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="16" t="n"/>
+      <c r="I9" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>8002</v>
+      </c>
+      <c r="K9" s="16" t="inlineStr">
+        <is>
+          <t>2:13:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>■ GX7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>형상</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>날수(F)</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>날경(Ø)</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>상크경(Ø)</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>코팅</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>특이사항</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>수량(개)</t>
+        </is>
+      </c>
+      <c r="J12" s="24" t="inlineStr">
+        <is>
+          <t>시간합계(초)</t>
+        </is>
+      </c>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>시간(H:M:S)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G13" s="26" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="H13" s="25" t="inlineStr"/>
+      <c r="I13" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="27" t="n">
+        <v>230</v>
+      </c>
+      <c r="K13" s="25" t="inlineStr">
+        <is>
+          <t>0:03:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="H14" s="25" t="inlineStr"/>
+      <c r="I14" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="27" t="n">
+        <v>178</v>
+      </c>
+      <c r="K14" s="25" t="inlineStr">
+        <is>
+          <t>0:02:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>NC_HSS</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G15" s="26" t="inlineStr">
+        <is>
+          <t>0141</t>
+        </is>
+      </c>
+      <c r="H15" s="25" t="inlineStr"/>
+      <c r="I15" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="27" t="n">
+        <v>370</v>
+      </c>
+      <c r="K15" s="25" t="inlineStr">
+        <is>
+          <t>0:06:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>NC_HSS</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G16" s="26" t="inlineStr">
+        <is>
+          <t>0141</t>
+        </is>
+      </c>
+      <c r="H16" s="25" t="inlineStr"/>
+      <c r="I16" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="27" t="n">
+        <v>415</v>
+      </c>
+      <c r="K16" s="25" t="inlineStr">
+        <is>
+          <t>0:06:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="J5" s="16" t="n">
-        <v>925</v>
-      </c>
-      <c r="K5" s="15" t="inlineStr">
-        <is>
-          <t>0:15:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>■ GX7</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>순서</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>형상</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>날수(F)</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>날경(Ø)</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="inlineStr">
-        <is>
-          <t>상크경(Ø)</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>코팅</t>
-        </is>
-      </c>
-      <c r="G8" s="23" t="inlineStr">
-        <is>
-          <t>특이사항</t>
-        </is>
-      </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I8" s="23" t="inlineStr">
-        <is>
-          <t>수량(개)</t>
-        </is>
-      </c>
-      <c r="J8" s="23" t="inlineStr">
-        <is>
-          <t>시간합계(초)</t>
-        </is>
-      </c>
-      <c r="K8" s="23" t="inlineStr">
-        <is>
-          <t>시간(H:M:S)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="24" t="n">
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="F17" s="26" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G17" s="26" t="inlineStr">
+        <is>
+          <t>0155 ㅋㅌ</t>
+        </is>
+      </c>
+      <c r="H17" s="25" t="inlineStr"/>
+      <c r="I17" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="25" t="inlineStr">
-        <is>
-          <t>드릴</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="n">
+      <c r="J17" s="27" t="n">
+        <v>405</v>
+      </c>
+      <c r="K17" s="25" t="inlineStr">
+        <is>
+          <t>0:06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E9" s="24" t="n">
+      <c r="D18" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="F18" s="26" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G18" s="26" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="H18" s="25" t="inlineStr"/>
+      <c r="I18" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" s="27" t="n">
+        <v>10800</v>
+      </c>
+      <c r="K18" s="25" t="inlineStr">
+        <is>
+          <t>3:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="E19" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G19" s="26" t="inlineStr">
+        <is>
+          <t>0165</t>
+        </is>
+      </c>
+      <c r="H19" s="25" t="inlineStr"/>
+      <c r="I19" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="27" t="n">
+        <v>321</v>
+      </c>
+      <c r="K19" s="25" t="inlineStr">
+        <is>
+          <t>0:05:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="D20" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="E20" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="F20" s="26" t="inlineStr">
         <is>
           <t>뮤</t>
         </is>
       </c>
-      <c r="G9" s="25" t="inlineStr">
-        <is>
-          <t>0168</t>
-        </is>
-      </c>
-      <c r="H9" s="24" t="inlineStr"/>
-      <c r="I9" s="26" t="n">
+      <c r="G20" s="26" t="inlineStr">
+        <is>
+          <t>0143</t>
+        </is>
+      </c>
+      <c r="H20" s="25" t="inlineStr"/>
+      <c r="I20" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="26" t="n">
-        <v>225</v>
-      </c>
-      <c r="K9" s="24" t="inlineStr">
-        <is>
-          <t>0:03:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="J20" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="25" t="inlineStr">
+        <is>
+          <t>0:00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>GX7 소계</t>
         </is>
       </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n"/>
-      <c r="I10" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="16" t="n">
-        <v>225</v>
-      </c>
-      <c r="K10" s="15" t="inlineStr">
-        <is>
-          <t>0:03:45</t>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="16" t="n"/>
+      <c r="H21" s="16" t="n"/>
+      <c r="I21" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="J21" s="17" t="n">
+        <v>12720</v>
+      </c>
+      <c r="K21" s="16" t="inlineStr">
+        <is>
+          <t>3:32:00</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A21:H21"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A11:K11"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
